--- a/ig/TEST-SUPPLEMENT/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-10-01</t>
+    <t>2025-11-06</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-01T00:00:00+00:00</t>
+    <t>2025-11-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41118</t>
+    <t>41206</t>
   </si>
   <si>
     <t>Code</t>
